--- a/Thesis Forecasting/metadata/rbfnn/testing_average_metrics.xlsx
+++ b/Thesis Forecasting/metadata/rbfnn/testing_average_metrics.xlsx
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>158</v>
+        <v>234</v>
       </c>
       <c r="D2" t="n">
-        <v>3.475919113707131</v>
+        <v>3.476164999616764</v>
       </c>
       <c r="E2" t="n">
-        <v>1.840847984937388</v>
+        <v>1.841105299238234</v>
       </c>
       <c r="F2" t="n">
-        <v>3.440295102101322</v>
+        <v>3.440686379843341</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8988599585985897</v>
+        <v>0.8988369512132961</v>
       </c>
     </row>
     <row r="3">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D3" t="n">
         <v>1.372393407127368</v>
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6106872916793786</v>
+        <v>0.6106872916782813</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6974508930056273</v>
+        <v>0.6974508930041152</v>
       </c>
       <c r="F4" t="n">
-        <v>3.077447039614186</v>
+        <v>3.07744703961429</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9453153141242143</v>
+        <v>0.9453153141242105</v>
       </c>
     </row>
     <row r="5">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D5" t="n">
         <v>4.039603029011061</v>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>171</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
         <v>1.404527208907398</v>
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D7" t="n">
-        <v>4.209301696521237</v>
+        <v>4.209301696541133</v>
       </c>
       <c r="E7" t="n">
-        <v>1.490988678325157</v>
+        <v>1.490988678326474</v>
       </c>
       <c r="F7" t="n">
-        <v>2.254351155379669</v>
+        <v>2.254351155380284</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9046698091595458</v>
+        <v>0.9046698091594937</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis Forecasting/metadata/rbfnn/testing_average_metrics.xlsx
+++ b/Thesis Forecasting/metadata/rbfnn/testing_average_metrics.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,37 +440,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>plant</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>feature_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MAPE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
